--- a/data/trans_orig/P37C2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37C2_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de que las vacunas son seguras en 2023</t>
+          <t>Población según la creencia de que las vacunas son seguras en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>316</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>11278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>2920</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12243</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11470</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>15959</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21356</t>
+          <t>21646</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18311</t>
+          <t>18946</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15719</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33262</t>
+          <t>33270</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>277338</t>
+          <t>276262</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>296788</t>
+          <t>296807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>264741</t>
+          <t>264938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277644</t>
+          <t>277007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>547536</t>
+          <t>547876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>571105</t>
+          <t>571325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27016</t>
+          <t>27350</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60211</t>
+          <t>60582</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16113</t>
+          <t>15802</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30363</t>
+          <t>31682</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48007</t>
+          <t>47955</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83648</t>
+          <t>85856</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>156038</t>
+          <t>156305</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211365</t>
+          <t>212764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>131030</t>
+          <t>130940</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169430</t>
+          <t>168872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>296752</t>
+          <t>299259</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>366598</t>
+          <t>369997</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263881</t>
+          <t>263350</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>322301</t>
+          <t>321454</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>315376</t>
+          <t>314905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354997</t>
+          <t>354996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>592313</t>
+          <t>592758</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>666406</t>
+          <t>662898</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,33%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>702</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>13005</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26808</t>
+          <t>27709</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9745</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23940</t>
+          <t>24197</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>22356</t>
+          <t>20962</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>43020</t>
+          <t>42522</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16509</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37212</t>
+          <t>34244</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>15474</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29493</t>
+          <t>31568</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35012</t>
+          <t>35779</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59934</t>
+          <t>59742</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251361</t>
+          <t>252512</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>278966</t>
+          <t>278403</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>291323</t>
+          <t>289630</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>310921</t>
+          <t>310660</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>550267</t>
+          <t>550360</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>584738</t>
+          <t>583733</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,91%</t>
         </is>
       </c>
     </row>
@@ -2776,97 +2776,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2486</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>567</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2852</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>567</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>2227</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -2889,97 +2889,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2254</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>419</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2211</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2215</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23918</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34700</t>
+          <t>33412</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>237447</t>
+          <t>214391</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>274032</t>
+          <t>249178</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>32,18%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>275896</t>
+          <t>279320</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>297049</t>
+          <t>297618</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>228121</t>
+          <t>243130</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>461895</t>
+          <t>461488</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>489803</t>
+          <t>486882</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>754359</t>
+          <t>753916</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -3458,97 +3458,97 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1217</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5925</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10240</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>20278</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>94205</t>
+          <t>94545</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>117347</t>
+          <t>115675</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>144830</t>
+          <t>144022</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>162456</t>
+          <t>162123</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>245667</t>
+          <t>244832</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>273944</t>
+          <t>274376</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,42%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>48044</t>
+          <t>49000</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>70538</t>
+          <t>69647</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>40160</t>
+          <t>40561</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>57073</t>
+          <t>58104</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>94557</t>
+          <t>94674</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>121567</t>
+          <t>121848</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>13410</t>
+          <t>12551</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14934</t>
+          <t>13920</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>803</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10825</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>21077</t>
+          <t>20287</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15582</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>33884</t>
+          <t>34465</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19465</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>26307</t>
+          <t>25970</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>48407</t>
+          <t>49396</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>30127</t>
+          <t>29327</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>53159</t>
+          <t>52072</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>23557</t>
+          <t>24067</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>40282</t>
+          <t>41424</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>59559</t>
+          <t>58196</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>88744</t>
+          <t>88189</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>178650</t>
+          <t>178934</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>206842</t>
+          <t>206204</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>196201</t>
+          <t>196688</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>217463</t>
+          <t>216885</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>381184</t>
+          <t>381436</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>417393</t>
+          <t>416668</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>17453</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>19708</t>
+          <t>20906</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>915</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5981</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>19111</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>28464</t>
+          <t>27789</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>55248</t>
+          <t>56410</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>24903</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>76446</t>
+          <t>75584</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>55300</t>
+          <t>56655</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>122387</t>
+          <t>120320</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>135653</t>
+          <t>136810</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>186932</t>
+          <t>188121</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>65774</t>
+          <t>71737</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>201969</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>199531</t>
+          <t>197913</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>371299</t>
+          <t>371303</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>378637</t>
+          <t>378890</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>432631</t>
+          <t>433620</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>556924</t>
+          <t>559096</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>748286</t>
+          <t>741149</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>954496</t>
+          <t>958393</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1182744</t>
+          <t>1190370</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,49%</t>
         </is>
       </c>
     </row>
@@ -5504,82 +5504,82 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>2336</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="R46" s="2" t="inlineStr">
         <is>
           <t>595</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>3279</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>17818</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>20924</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>17874</t>
+          <t>20245</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>64208</t>
+          <t>66938</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>57264</t>
+          <t>54335</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>48056</t>
+          <t>48878</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>103776</t>
+          <t>103900</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>69876</t>
+          <t>60662</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>225269</t>
+          <t>226221</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>127735</t>
+          <t>125243</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>163367</t>
+          <t>163013</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>187331</t>
+          <t>191244</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>366919</t>
+          <t>367266</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>631714</t>
+          <t>627230</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>831056</t>
+          <t>844612</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>507303</t>
+          <t>508293</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>551156</t>
+          <t>551282</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1163461</t>
+          <t>1163378</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1398798</t>
+          <t>1397438</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,08%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>22148</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,47 +6201,47 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>6149</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>22130</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>11948</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>21095</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>14807</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>36024</t>
+          <t>36592</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>25343</t>
+          <t>26297</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>50611</t>
+          <t>52037</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13296</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>30634</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>43826</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>71987</t>
+          <t>73593</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>145616</t>
+          <t>145680</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>222411</t>
+          <t>220376</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>123048</t>
+          <t>123261</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>180560</t>
+          <t>184498</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>289007</t>
+          <t>285418</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>389005</t>
+          <t>382375</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>541800</t>
+          <t>544855</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>763313</t>
+          <t>767920</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>624402</t>
+          <t>633279</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>910616</t>
+          <t>914965</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1254981</t>
+          <t>1242645</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1619107</t>
+          <t>1582515</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2418497</t>
+          <t>2417162</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2704114</t>
+          <t>2711381</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2563167</t>
+          <t>2572038</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2857237</t>
+          <t>2855380</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>5046842</t>
+          <t>5079816</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5461346</t>
+          <t>5479821</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,48%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C2_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37C2_2023-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>668</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5615</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>962</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,22 +908,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -951,27 +951,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1785</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>12256</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>7094</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15959</t>
+          <t>16399</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>10456</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21646</t>
+          <t>18196</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11783</t>
+          <t>12477</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18946</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23093</t>
+          <t>22932</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33270</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>289180</t>
+          <t>296788</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>276262</t>
+          <t>286809</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>296807</t>
+          <t>303696</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>272293</t>
+          <t>297408</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>264938</t>
+          <t>290884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277007</t>
+          <t>303118</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>561473</t>
+          <t>594197</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>547876</t>
+          <t>581173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>571325</t>
+          <t>603464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>309885</t>
+          <t>317609</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>309885</t>
+          <t>317609</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>309885</t>
+          <t>317609</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>289142</t>
+          <t>315574</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289142</t>
+          <t>315574</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289142</t>
+          <t>315574</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>599027</t>
+          <t>633183</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>599027</t>
+          <t>633183</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>599027</t>
+          <t>633183</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,49 +1452,49 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2720</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>7938</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2778</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>8602</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,05%</t>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39959</t>
+          <t>39645</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27350</t>
+          <t>27073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60582</t>
+          <t>56323</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22643</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15802</t>
+          <t>16591</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31682</t>
+          <t>32107</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>62602</t>
+          <t>63508</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47955</t>
+          <t>47927</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>85856</t>
+          <t>80812</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>183227</t>
+          <t>188169</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>156305</t>
+          <t>163109</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>212764</t>
+          <t>219164</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>149368</t>
+          <t>160238</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>130940</t>
+          <t>141031</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>168872</t>
+          <t>178775</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>332595</t>
+          <t>348407</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>299259</t>
+          <t>314291</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>369997</t>
+          <t>381572</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>292711</t>
+          <t>300422</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263350</t>
+          <t>269140</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>321454</t>
+          <t>327467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>335870</t>
+          <t>354864</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>314905</t>
+          <t>335138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354996</t>
+          <t>374263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>628581</t>
+          <t>655285</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>592758</t>
+          <t>621440</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>662898</t>
+          <t>692554</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,5%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>513006</t>
+          <t>544015</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>513006</t>
+          <t>544015</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>513006</t>
+          <t>544015</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1030399</t>
+          <t>1073674</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1030399</t>
+          <t>1073674</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1030399</t>
+          <t>1073674</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,22 +2159,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5378</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,17 +2237,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>491</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7021</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>25187</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>25661</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>31045</t>
+          <t>32200</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20962</t>
+          <t>23226</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>42522</t>
+          <t>45466</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24521</t>
+          <t>27488</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>19005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34244</t>
+          <t>39559</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21786</t>
+          <t>22346</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15474</t>
+          <t>15396</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31568</t>
+          <t>31081</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>46308</t>
+          <t>49834</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35779</t>
+          <t>38446</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59742</t>
+          <t>62978</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>266924</t>
+          <t>264398</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252512</t>
+          <t>248819</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>278403</t>
+          <t>276481</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>302030</t>
+          <t>309506</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>289630</t>
+          <t>297125</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>310660</t>
+          <t>318871</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>568953</t>
+          <t>573904</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>550360</t>
+          <t>554667</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>583733</t>
+          <t>589548</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>314379</t>
+          <t>314374</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>314379</t>
+          <t>314374</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>314379</t>
+          <t>314374</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>342162</t>
+          <t>351499</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>342162</t>
+          <t>351499</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>342162</t>
+          <t>351499</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>656540</t>
+          <t>665872</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>656540</t>
+          <t>665872</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>656540</t>
+          <t>665872</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>470</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>470</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21765</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21726</t>
+          <t>22952</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>27542</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>17139</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33412</t>
+          <t>48632</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>72994</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>214391</t>
+          <t>9471</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>74159</t>
+          <t>6253</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>249178</t>
+          <t>11658</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>291541</t>
+          <t>335047</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>279320</t>
+          <t>315068</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>297618</t>
+          <t>344197</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>390868</t>
+          <t>402689</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>243130</t>
+          <t>389249</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>461488</t>
+          <t>408948</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>682409</t>
+          <t>737737</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>486882</t>
+          <t>716539</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>753916</t>
+          <t>749127</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>302391</t>
+          <t>355336</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>302391</t>
+          <t>355336</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>302391</t>
+          <t>355336</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>471840</t>
+          <t>417999</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>471840</t>
+          <t>417999</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>471840</t>
+          <t>417999</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>774232</t>
+          <t>773335</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>774232</t>
+          <t>773335</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>774232</t>
+          <t>773335</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>9838</t>
+          <t>10837</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7354</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20278</t>
+          <t>23532</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>105561</t>
+          <t>121663</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>94545</t>
+          <t>107946</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>115675</t>
+          <t>132349</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>154006</t>
+          <t>167232</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>144022</t>
+          <t>156476</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>162123</t>
+          <t>176100</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>259567</t>
+          <t>288895</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>244832</t>
+          <t>272514</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>274376</t>
+          <t>303780</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,71%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>59374</t>
+          <t>67119</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>57402</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>69647</t>
+          <t>80734</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>48459</t>
+          <t>52703</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>40561</t>
+          <t>44853</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>58104</t>
+          <t>62700</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>107833</t>
+          <t>119823</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>94674</t>
+          <t>104792</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>121848</t>
+          <t>135095</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>176288</t>
+          <t>203226</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>176288</t>
+          <t>203226</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>176288</t>
+          <t>203226</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>207862</t>
+          <t>226392</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>207862</t>
+          <t>226392</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>207862</t>
+          <t>226392</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>384150</t>
+          <t>429618</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>384150</t>
+          <t>429618</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>384150</t>
+          <t>429618</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>611</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1705</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3887</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>15027</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>738</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>9162</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>11862</t>
+          <t>11730</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>23355</t>
+          <t>23724</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15595</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>34465</t>
+          <t>33801</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>13323</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>7891</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>20175</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>35759</t>
+          <t>37047</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>27655</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>49396</t>
+          <t>48829</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>40422</t>
+          <t>42280</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>29327</t>
+          <t>32442</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>52072</t>
+          <t>55274</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>31942</t>
+          <t>34031</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>24067</t>
+          <t>25894</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>41424</t>
+          <t>43395</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>72364</t>
+          <t>76310</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>58196</t>
+          <t>62070</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>88189</t>
+          <t>90777</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>193163</t>
+          <t>192722</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>178934</t>
+          <t>177666</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>206204</t>
+          <t>206104</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>206913</t>
+          <t>210639</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>196688</t>
+          <t>197469</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>216885</t>
+          <t>220305</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>400075</t>
+          <t>403360</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>381436</t>
+          <t>386818</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>416668</t>
+          <t>420640</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>78,92%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>255579</t>
+          <t>262304</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>255579</t>
+          <t>262304</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>255579</t>
+          <t>262304</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>525215</t>
+          <t>533011</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>525215</t>
+          <t>533011</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>525215</t>
+          <t>533011</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>7234</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>15411</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>10052</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>20906</t>
+          <t>20645</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>6700</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13985</t>
+          <t>21676</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>5123</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>10979</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>9651</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>19861</t>
+          <t>27423</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>40320</t>
+          <t>46185</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>27789</t>
+          <t>32481</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>56410</t>
+          <t>63713</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>52269</t>
+          <t>60448</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>24903</t>
+          <t>47138</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>75584</t>
+          <t>75980</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>92589</t>
+          <t>106633</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>56655</t>
+          <t>85129</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>120320</t>
+          <t>130803</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>160152</t>
+          <t>189780</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>136810</t>
+          <t>161871</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>188121</t>
+          <t>219086</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>146102</t>
+          <t>174115</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>71737</t>
+          <t>152518</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>197961</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>306254</t>
+          <t>363895</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>197913</t>
+          <t>331842</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>371303</t>
+          <t>399990</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>406673</t>
+          <t>459989</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>378890</t>
+          <t>427354</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>433620</t>
+          <t>487205</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>634271</t>
+          <t>517743</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>559096</t>
+          <t>493357</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>741149</t>
+          <t>543281</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1040944</t>
+          <t>977732</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>958393</t>
+          <t>937879</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1190370</t>
+          <t>1013950</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>68,72%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>617294</t>
+          <t>710879</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>617294</t>
+          <t>710879</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>617294</t>
+          <t>710879</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>843524</t>
+          <t>764662</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>843524</t>
+          <t>764662</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>843524</t>
+          <t>764662</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1460818</t>
+          <t>1475541</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1460818</t>
+          <t>1475541</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1460818</t>
+          <t>1475541</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>688</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>688</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>10522</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>5164</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>17039</t>
+          <t>18269</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8401</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>14800</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>21949</t>
+          <t>23668</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>43108</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>20245</t>
+          <t>36376</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>66938</t>
+          <t>65907</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>35995</t>
+          <t>37076</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>27738</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>54335</t>
+          <t>48898</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>79103</t>
+          <t>86821</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>48878</t>
+          <t>70576</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>103900</t>
+          <t>106498</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>159294</t>
+          <t>191062</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>60662</t>
+          <t>163395</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>226221</t>
+          <t>218617</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>143343</t>
+          <t>169174</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>125243</t>
+          <t>149102</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>163013</t>
+          <t>193207</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>302638</t>
+          <t>360237</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>191244</t>
+          <t>330454</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>367266</t>
+          <t>399101</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>715365</t>
+          <t>544973</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>627230</t>
+          <t>514935</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>844612</t>
+          <t>572741</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>531646</t>
+          <t>619393</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>508293</t>
+          <t>596524</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>551282</t>
+          <t>642078</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>1247011</t>
+          <t>1164366</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1163378</t>
+          <t>1127462</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1397438</t>
+          <t>1200173</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>73,77%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>927177</t>
+          <t>796303</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>927177</t>
+          <t>796303</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>927177</t>
+          <t>796303</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1642569</t>
+          <t>1626911</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1642569</t>
+          <t>1626911</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1642569</t>
+          <t>1626911</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,102 +6181,102 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>21138</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>13719</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>7704</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>23139</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>25098</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>16415</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>37097</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>11948</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>6149</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>22130</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>24004</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>14807</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>36592</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>37186</t>
+          <t>42879</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>26297</t>
+          <t>31780</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>52037</t>
+          <t>57825</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,27 +6329,27 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>30634</t>
+          <t>31231</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>57137</t>
+          <t>64404</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>43826</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>73593</t>
+          <t>80757</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>184619</t>
+          <t>210190</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>145680</t>
+          <t>179670</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>220376</t>
+          <t>243005</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>152932</t>
+          <t>168289</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>123261</t>
+          <t>146101</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>184498</t>
+          <t>195503</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>337550</t>
+          <t>378479</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>285418</t>
+          <t>340740</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>382375</t>
+          <t>421575</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>685652</t>
+          <t>772187</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>544855</t>
+          <t>718689</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>767920</t>
+          <t>828294</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>731326</t>
+          <t>744575</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>633279</t>
+          <t>701194</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>914965</t>
+          <t>788062</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>1416978</t>
+          <t>1516762</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1242645</t>
+          <t>1446286</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1582515</t>
+          <t>1581154</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>2514931</t>
+          <t>2461459</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2417162</t>
+          <t>2396453</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2711381</t>
+          <t>2523718</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2722349</t>
+          <t>2764944</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2572038</t>
+          <t>2713611</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2855380</t>
+          <t>2814299</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>5237280</t>
+          <t>5226403</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>5079816</t>
+          <t>5151168</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5479821</t>
+          <t>5304047</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>3434444</t>
+          <t>3498094</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3434444</t>
+          <t>3498094</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>3434444</t>
+          <t>3498094</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3638506</t>
+          <t>3713052</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3638506</t>
+          <t>3713052</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3638506</t>
+          <t>3713052</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>7072950</t>
+          <t>7211146</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>7072950</t>
+          <t>7211146</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>7072950</t>
+          <t>7211146</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
